--- a/resultados/altamiradoparana/erros_varredura.xlsx
+++ b/resultados/altamiradoparana/erros_varredura.xlsx
@@ -456,23 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.altamiradoparana.pr.gov.br/mapa-site-xml</t>
+          <t>https://altamiradoparana.pr.gov.br/pagina/240_Processo-Seletivo-Simplificado-032025-Editais.html</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-29 10:24:34</t>
+          <t>2026-07-29 10:25:17</t>
         </is>
       </c>
     </row>
@@ -484,23 +484,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.altamiradoparana.pr.gov.br/page_carta_de_servicos_individual?tipo_id=1&amp;carta_id=4&amp;categoria_id=1</t>
+          <t>https://altamiradoparana.pr.gov.br/site/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29 10:25:07</t>
+          <t>2026-07-29 10:25:19</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://altamiradoparana.pr.gov.br/pagina/240_Processo-Seletivo-Simplificado-032025-Editais.html</t>
+          <t>https://www.altamiradoparana.pr.gov.br/pagina/227_CHAMADA-PUBLICA-PNAE.html</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -524,11 +524,11 @@
         <v>404</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-29 10:25:17</t>
+          <t>2026-07-29 10:26:30</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://altamiradoparana.pr.gov.br/site/</t>
+          <t>http://www.altamiradoparana.pr.gov.br/pagina/167_PLANO-EMERGENCIAL-DE-RETOMADA-DO-DESENVOLVIMENTO-ECONOMICO-LOCAL.html</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -552,11 +552,11 @@
         <v>404</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-29 10:25:19</t>
+          <t>2026-07-29 10:27:47</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.altamiradoparana.pr.gov.br/pagina/227_CHAMADA-PUBLICA-PNAE.html</t>
+          <t>https://www.altamiradoparana.pr.gov.br/pagina/235_LEILAO.html?fbclid=IwZXh0bgNhZW0CMTAAAR2epIMqlDM7e6kcCesRwglSXw5sXMfs6RXb2tSrRf7BYrcvpZsIvkWN-Fk_aem_AXrku9P1z8vX3AQIiik-RB_6nJUGp227LmgfDYRz5BARY2YWRr8YnedMRK1fNK2iH8RgbeeCEp6D2rPCuw5fFy3O</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -580,11 +580,11 @@
         <v>404</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-29 10:26:30</t>
+          <t>2026-07-29 10:28:20</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://altamiradoparana.pr.gov.br/mapa-site-xml</t>
+          <t>http://www.altamiradoparana.pr.gov.br/pagina/176_DEPARTAMENTO-DE-CULTURA.html</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-29 10:27:25</t>
+          <t>2026-07-29 10:28:28</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>http://www.altamiradoparana.pr.gov.br/pagina/167_PLANO-EMERGENCIAL-DE-RETOMADA-DO-DESENVOLVIMENTO-ECONOMICO-LOCAL.html</t>
+          <t>http://altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -636,11 +636,11 @@
         <v>404</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-29 10:27:47</t>
+          <t>2026-07-29 10:30:07</t>
         </is>
       </c>
     </row>
@@ -652,23 +652,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://altamiradoparana.pr.gov.br/page_carta_de_servicos_individual?tipo_id=1&amp;carta_id=4&amp;categoria_id=1</t>
+          <t>http://altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html?fbclid=IwAR3BjEo54g0AeN9-zy6TjX5fm8KubV94E1tp7UUTvEs0-_WzpkHPPTlzULE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-29 10:28:12</t>
+          <t>2026-07-29 10:30:08</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.altamiradoparana.pr.gov.br/pagina/235_LEILAO.html?fbclid=IwZXh0bgNhZW0CMTAAAR2epIMqlDM7e6kcCesRwglSXw5sXMfs6RXb2tSrRf7BYrcvpZsIvkWN-Fk_aem_AXrku9P1z8vX3AQIiik-RB_6nJUGp227LmgfDYRz5BARY2YWRr8YnedMRK1fNK2iH8RgbeeCEp6D2rPCuw5fFy3O</t>
+          <t>http://altamiradoparana.pr.gov.br/noticiasView/?id=125&amp;fbclid=IwAR0i0IWemlpdPcgf3PIVljVxEm_RO7V0k-H9kNTklTucmggTMcAMLDAsVnI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -692,11 +692,11 @@
         <v>404</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-29 10:28:20</t>
+          <t>2026-07-29 10:30:09</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>http://www.altamiradoparana.pr.gov.br/pagina/176_DEPARTAMENTO-DE-CULTURA.html</t>
+          <t>https://www.altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -720,11 +720,11 @@
         <v>404</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-29 10:28:28</t>
+          <t>2026-07-29 10:30:13</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>http://altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html</t>
+          <t>http://altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html?fbclid=IwAR1IgPqtNbH3MFo1QICekG5mfq0VwRH-7L-ee_q07remLErhqSUZspjR8DM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-29 10:30:07</t>
+          <t>2026-07-29 10:30:13</t>
         </is>
       </c>
     </row>
@@ -764,23 +764,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>http://altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html?fbclid=IwAR3BjEo54g0AeN9-zy6TjX5fm8KubV94E1tp7UUTvEs0-_WzpkHPPTlzULE</t>
+          <t>https://www.altamiradoparana.pr.gov.br/mapa-site-xml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-29 10:30:08</t>
+          <t>2026-07-30 01:19:22</t>
         </is>
       </c>
     </row>
@@ -792,23 +792,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>http://altamiradoparana.pr.gov.br/noticiasView/?id=125&amp;fbclid=IwAR0i0IWemlpdPcgf3PIVljVxEm_RO7V0k-H9kNTklTucmggTMcAMLDAsVnI</t>
+          <t>https://www.altamiradoparana.pr.gov.br/page_carta_de_servicos_individual?tipo_id=1&amp;carta_id=4&amp;categoria_id=1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-29 10:30:09</t>
+          <t>2026-07-30 01:19:27</t>
         </is>
       </c>
     </row>
@@ -820,23 +820,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html</t>
+          <t>https://altamiradoparana.pr.gov.br/mapa-site-xml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-29 10:30:13</t>
+          <t>2026-07-30 01:19:32</t>
         </is>
       </c>
     </row>
@@ -848,23 +848,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>http://altamiradoparana.pr.gov.br/pagina/187_Consulta-Publica-Plano-Diretor.html?fbclid=IwAR1IgPqtNbH3MFo1QICekG5mfq0VwRH-7L-ee_q07remLErhqSUZspjR8DM</t>
+          <t>https://altamiradoparana.pr.gov.br/page_carta_de_servicos_individual?tipo_id=1&amp;carta_id=4&amp;categoria_id=1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-29 10:30:13</t>
+          <t>2026-07-30 01:19:37</t>
         </is>
       </c>
     </row>
